--- a/web_design_forms/023_user_interface_design_checklist--web_design_forms.xlsx
+++ b/web_design_forms/023_user_interface_design_checklist--web_design_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Overall Feel and Looking</t>
+          <t>Overall Feel And Looking Label</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Content Strategy</t>
+          <t>Content Strategy Label</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>visual_hierarchy</t>
+          <t>visual_hierarchy_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Visual Hierarchy</t>
+          <t>Visual Hierarchy 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Color Usage</t>
+          <t>Color Usage Label</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -851,7 +851,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Overall Feeling</t>
+          <t>Overall Feeling Label</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1070,7 +1070,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>visual_hierarchy_choices</t>
+          <t>visual_hierarchy_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1087,7 +1087,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>visual_hierarchy_choices</t>
+          <t>visual_hierarchy_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
